--- a/backend/singlenet_irrigation_system.xlsx
+++ b/backend/singlenet_irrigation_system.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,66 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ground Kit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>77100-005880</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ground Kit</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GS-ONE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>74715-000010</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GS-ONE W.EXT.SOLAR-PANEL-4.4W+5M-RF-CABLE Monitoring unit</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NETACAP 6/60CM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>74730-000009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOIL MOISTURE NETACAP WP 6/60CM</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/singlenet_irrigation_system.xlsx
+++ b/backend/singlenet_irrigation_system.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -663,46 +663,6 @@
       </c>
       <c r="D8" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GS-ONE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>74715-000010</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GS-ONE W.EXT.SOLAR-PANEL-4.4W+5M-RF-CABLE Monitoring unit</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NETACAP 6/60CM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>74730-000009</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SOIL MOISTURE NETACAP WP 6/60CM</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
